--- a/input/mapping/075. OCB_GOLD_TCKH_TXN_TP_DIM_HOP.xlsx
+++ b/input/mapping/075. OCB_GOLD_TCKH_TXN_TP_DIM_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1747" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36CE0E8A-770F-401B-A266-D020465AB99D}"/>
+  <xr:revisionPtr revIDLastSave="1750" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{369A01C9-7870-4D5F-AA67-A8B3022E0F16}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -126,13 +126,6 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS TXN_TP_DIM (
-    TXN_TP_DW_ID    STRING,
-    TXN_TP_NM_EN    STRING,
-    TXN_TP_NM_VN    STRING,
-    TXN_TP_ID       STRING
-)
-USING DELTA;
 TRUNCATE TABLE TXN_TP_DIM;
 INSERT INTO TXN_TP_DIM (
     TXN_TP_DW_ID,
@@ -161,8 +154,7 @@
     TXN_TP_NM_EN,
     TXN_TP_NM_VN,
     TXN_TP_ID
-FROM cte_cv
-;</t>
+FROM cte_cv</t>
   </si>
   <si>
     <t>JOIN SCHEMA</t>
@@ -2914,9 +2906,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
@@ -7268,7 +7258,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -12076,6 +12066,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -12247,15 +12246,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12267,11 +12257,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
